--- a/excels/negociaciones_scrapp.xlsx
+++ b/excels/negociaciones_scrapp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conasamigobmx-my.sharepoint.com/personal/hector_soto_conasami_gob_mx/Documents/Escritorio/Negociación laboral/excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conasamigobmx-my.sharepoint.com/personal/hector_soto_conasami_gob_mx/Documents/Escritorio/CAEL/Informes/Negociación laboral/excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="11_C9AD68BD0E089C5FE78170FC14B787A8F2562299" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4393F9AD-D03B-4D42-8CF6-533A2300FDE9}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="11_C9AD68BD0E089C5FE78170FC14B787A8F2562299" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{264AC878-58D2-4F3E-8EC4-8D625BB45844}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -245,7 +245,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
@@ -255,6 +255,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
@@ -4052,6 +4053,197 @@
       <c r="AJ45" s="4">
         <v>23</v>
       </c>
+    </row>
+    <row r="46" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A46" s="5">
+        <v>46023</v>
+      </c>
+      <c r="B46">
+        <v>2026</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2</v>
+      </c>
+      <c r="G46" s="4">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4">
+        <v>8</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4">
+        <v>5</v>
+      </c>
+      <c r="L46" s="4">
+        <v>11</v>
+      </c>
+      <c r="M46" s="4">
+        <v>4</v>
+      </c>
+      <c r="N46" s="4">
+        <v>7</v>
+      </c>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>2</v>
+      </c>
+      <c r="R46" s="4">
+        <v>15</v>
+      </c>
+      <c r="S46" s="4">
+        <v>2</v>
+      </c>
+      <c r="T46" s="4">
+        <v>4</v>
+      </c>
+      <c r="U46" s="4">
+        <v>1</v>
+      </c>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4">
+        <v>1</v>
+      </c>
+      <c r="X46" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y46" s="4">
+        <v>17</v>
+      </c>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="4">
+        <v>4</v>
+      </c>
+      <c r="AD46" s="4"/>
+      <c r="AE46" s="4">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG46" s="4">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="4"/>
+      <c r="AI46" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ46" s="4">
+        <v>20</v>
+      </c>
+      <c r="AK46" s="4"/>
+    </row>
+    <row r="47" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A47" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B47">
+        <v>2026</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4">
+        <v>2</v>
+      </c>
+      <c r="J47" s="4">
+        <v>2</v>
+      </c>
+      <c r="K47" s="4">
+        <v>3</v>
+      </c>
+      <c r="L47" s="4">
+        <v>4</v>
+      </c>
+      <c r="M47" s="4">
+        <v>3</v>
+      </c>
+      <c r="N47" s="4">
+        <v>7</v>
+      </c>
+      <c r="O47" s="4">
+        <v>1</v>
+      </c>
+      <c r="P47" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>1</v>
+      </c>
+      <c r="R47" s="4">
+        <v>15</v>
+      </c>
+      <c r="S47" s="4">
+        <v>3</v>
+      </c>
+      <c r="T47" s="4">
+        <v>4</v>
+      </c>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4">
+        <v>1</v>
+      </c>
+      <c r="W47" s="4">
+        <v>1</v>
+      </c>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4">
+        <v>6</v>
+      </c>
+      <c r="AB47" s="4"/>
+      <c r="AC47" s="4">
+        <v>2</v>
+      </c>
+      <c r="AD47" s="4">
+        <v>2</v>
+      </c>
+      <c r="AE47" s="4">
+        <v>2</v>
+      </c>
+      <c r="AF47" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="4">
+        <v>7</v>
+      </c>
+      <c r="AH47" s="4"/>
+      <c r="AI47" s="4">
+        <v>4</v>
+      </c>
+      <c r="AJ47" s="4">
+        <v>12</v>
+      </c>
+      <c r="AK47" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK38">

--- a/excels/negociaciones_scrapp.xlsx
+++ b/excels/negociaciones_scrapp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conasamigobmx-my.sharepoint.com/personal/hector_soto_conasami_gob_mx/Documents/Escritorio/CAEL/Informes/Negociación laboral/excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="11_C9AD68BD0E089C5FE78170FC14B787A8F2562299" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{264AC878-58D2-4F3E-8EC4-8D625BB45844}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="11_C9AD68BD0E089C5FE78170FC14B787A8F2562299" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2422C865-3338-40F5-8570-36FF26402E9F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emplazamientos_entidad" sheetId="1" r:id="rId1"/>
@@ -553,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK47"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
@@ -4244,6 +4244,173 @@
         <v>12</v>
       </c>
       <c r="AK47" s="4"/>
+    </row>
+    <row r="48" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A48" s="5">
+        <v>46082</v>
+      </c>
+      <c r="B48">
+        <v>2026</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4">
+        <v>2</v>
+      </c>
+      <c r="H48" s="4">
+        <v>8</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4">
+        <v>1</v>
+      </c>
+      <c r="K48" s="4">
+        <v>3</v>
+      </c>
+      <c r="L48" s="4">
+        <v>5</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4">
+        <v>5</v>
+      </c>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4">
+        <v>2</v>
+      </c>
+      <c r="R48" s="4">
+        <v>18</v>
+      </c>
+      <c r="S48" s="4">
+        <v>1</v>
+      </c>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4">
+        <v>1</v>
+      </c>
+      <c r="W48" s="4">
+        <v>1</v>
+      </c>
+      <c r="X48" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="4">
+        <v>10</v>
+      </c>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="4">
+        <v>4</v>
+      </c>
+      <c r="AD48" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="4">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="4">
+        <v>4</v>
+      </c>
+      <c r="AG48" s="4">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI48" s="4"/>
+      <c r="AJ48" s="4">
+        <v>14</v>
+      </c>
+      <c r="AK48" s="4"/>
+    </row>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="A49" s="5">
+        <v>46113</v>
+      </c>
+      <c r="B49">
+        <v>2026</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4">
+        <v>1</v>
+      </c>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4">
+        <v>1</v>
+      </c>
+      <c r="L49" s="4">
+        <v>3</v>
+      </c>
+      <c r="M49" s="4">
+        <v>3</v>
+      </c>
+      <c r="N49" s="4">
+        <v>3</v>
+      </c>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4">
+        <v>6</v>
+      </c>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4">
+        <v>1</v>
+      </c>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4">
+        <v>1</v>
+      </c>
+      <c r="X49" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="4">
+        <v>9</v>
+      </c>
+      <c r="Z49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4">
+        <v>3</v>
+      </c>
+      <c r="AF49" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG49" s="4">
+        <v>9</v>
+      </c>
+      <c r="AH49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ49" s="4">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK38">
